--- a/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,13 +706,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45202.6085204419</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,19 +751,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="E25" s="7" t="n"/>
     </row>
@@ -930,8 +913,6 @@
       <c r="A35" s="4" t="n"/>
       <c r="E35" s="7" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -942,18 +923,18 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
